--- a/artfynd/A 21370-2025 artfynd.xlsx
+++ b/artfynd/A 21370-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ10"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>91992991</v>
+        <v>136828020</v>
       </c>
       <c r="B2" t="n">
-        <v>79084</v>
+        <v>92292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Jämtlands län, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>412616</v>
+        <v>412592</v>
       </c>
       <c r="R2" t="n">
-        <v>6966018</v>
+        <v>6965947</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-06-01</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-10-31</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,31 +765,27 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91992991</t>
+          <t>https://artportalen.se/Sighting/136828020</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126348497</v>
+        <v>136828015</v>
       </c>
       <c r="B3" t="n">
-        <v>57953</v>
+        <v>93423</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>4366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Digerberget, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>412701</v>
+        <v>412878</v>
       </c>
       <c r="R3" t="n">
-        <v>6965749</v>
+        <v>6965808</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -851,17 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -876,65 +867,65 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348497</t>
+          <t>https://artportalen.se/Sighting/136828015</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126348498</v>
+        <v>136828019</v>
       </c>
       <c r="B4" t="n">
-        <v>57953</v>
+        <v>92076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Digerberget, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>412636</v>
+        <v>412577</v>
       </c>
       <c r="R4" t="n">
-        <v>6965623</v>
+        <v>6965950</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -958,17 +949,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -983,65 +969,65 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348498</t>
+          <t>https://artportalen.se/Sighting/136828019</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126348499</v>
+        <v>136828023</v>
       </c>
       <c r="B5" t="n">
-        <v>57953</v>
+        <v>79476</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Digerberget, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>412630</v>
+        <v>412364</v>
       </c>
       <c r="R5" t="n">
-        <v>6965613</v>
+        <v>6965991</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1065,17 +1051,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1090,27 +1071,27 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348499</t>
+          <t>https://artportalen.se/Sighting/136828023</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126348500</v>
+        <v>136828021</v>
       </c>
       <c r="B6" t="n">
-        <v>57953</v>
+        <v>78879</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1118,37 +1099,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Digerberget, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>412646</v>
+        <v>412533</v>
       </c>
       <c r="R6" t="n">
-        <v>6965606</v>
+        <v>6965932</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1172,17 +1153,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1197,27 +1173,27 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348500</t>
+          <t>https://artportalen.se/Sighting/136828021</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126348501</v>
+        <v>91992991</v>
       </c>
       <c r="B7" t="n">
-        <v>57953</v>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1225,37 +1201,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Digerberget, Hjd</t>
+          <t>Jämtlands län, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>412693</v>
+        <v>412616</v>
       </c>
       <c r="R7" t="n">
-        <v>6965664</v>
+        <v>6966018</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1279,17 +1255,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2018-06-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2018-10-31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1304,65 +1275,69 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348501</t>
+          <t>https://artportalen.se/Sighting/91992991</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126348502</v>
+        <v>136828022</v>
       </c>
       <c r="B8" t="n">
-        <v>57953</v>
+        <v>80595</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Digerberget, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>412740</v>
+        <v>412377</v>
       </c>
       <c r="R8" t="n">
-        <v>6965691</v>
+        <v>6965984</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1386,17 +1361,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1411,24 +1381,24 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348502</t>
+          <t>https://artportalen.se/Sighting/136828022</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126348503</v>
+        <v>126348497</v>
       </c>
       <c r="B9" t="n">
         <v>57953</v>
@@ -1463,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>412816</v>
+        <v>412701</v>
       </c>
       <c r="R9" t="n">
-        <v>6965745</v>
+        <v>6965749</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1503,7 +1473,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1529,13 +1499,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348503</t>
+          <t>https://artportalen.se/Sighting/126348497</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126348505</v>
+        <v>126348498</v>
       </c>
       <c r="B10" t="n">
         <v>57953</v>
@@ -1570,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>412820</v>
+        <v>412636</v>
       </c>
       <c r="R10" t="n">
-        <v>6965733</v>
+        <v>6965623</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1610,7 +1580,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1636,7 +1606,1062 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/126348498</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126348499</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Digerberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>412630</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6965613</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348499</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126348500</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Digerberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>412646</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6965606</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348500</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126348501</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Digerberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>412693</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6965664</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348501</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>126348502</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Digerberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>412740</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6965691</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348502</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>126348503</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Digerberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>412816</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6965745</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348503</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>126348505</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Digerberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>412820</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6965733</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/126348505</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>136828018</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>412709</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6965881</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828018</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136828014</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79499</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>412914</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6965758</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828014</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136828017</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79499</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>412708</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6965886</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828017</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>136828024</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79499</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>412344</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6966001</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828024</t>
         </is>
       </c>
     </row>
@@ -1651,6 +2676,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21370-2025 artfynd.xlsx
+++ b/artfynd/A 21370-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ20"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>136828020</v>
+        <v>91992991</v>
       </c>
       <c r="B2" t="n">
-        <v>92292</v>
+        <v>79084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Jämtlands län, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>412592</v>
+        <v>412616</v>
       </c>
       <c r="R2" t="n">
-        <v>6965947</v>
+        <v>6966018</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2018-06-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2018-10-31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,27 +765,31 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136828020</t>
+          <t>https://artportalen.se/Sighting/91992991</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136828015</v>
+        <v>126348497</v>
       </c>
       <c r="B3" t="n">
-        <v>93423</v>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,37 +797,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4366</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Digerberget, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>412878</v>
+        <v>412701</v>
       </c>
       <c r="R3" t="n">
-        <v>6965808</v>
+        <v>6965749</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +851,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,65 +876,65 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136828015</t>
+          <t>https://artportalen.se/Sighting/126348497</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136828019</v>
+        <v>126348498</v>
       </c>
       <c r="B4" t="n">
-        <v>92076</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Digerberget, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>412577</v>
+        <v>412636</v>
       </c>
       <c r="R4" t="n">
-        <v>6965950</v>
+        <v>6965623</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -949,12 +958,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,65 +983,65 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136828019</t>
+          <t>https://artportalen.se/Sighting/126348498</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136828023</v>
+        <v>126348499</v>
       </c>
       <c r="B5" t="n">
-        <v>79476</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Digerberget, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>412364</v>
+        <v>412630</v>
       </c>
       <c r="R5" t="n">
-        <v>6965991</v>
+        <v>6965613</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,12 +1065,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,27 +1090,27 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136828023</t>
+          <t>https://artportalen.se/Sighting/126348499</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136828021</v>
+        <v>126348500</v>
       </c>
       <c r="B6" t="n">
-        <v>78879</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,37 +1118,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Digerberget, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>412533</v>
+        <v>412646</v>
       </c>
       <c r="R6" t="n">
-        <v>6965932</v>
+        <v>6965606</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1153,12 +1172,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,27 +1197,27 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136828021</t>
+          <t>https://artportalen.se/Sighting/126348500</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>91992991</v>
+        <v>126348501</v>
       </c>
       <c r="B7" t="n">
-        <v>79084</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,37 +1225,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Jämtlands län, Hjd</t>
+          <t>Digerberget, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>412616</v>
+        <v>412693</v>
       </c>
       <c r="R7" t="n">
-        <v>6966018</v>
+        <v>6965664</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1255,12 +1279,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2018-06-01</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2018-10-31</t>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1275,69 +1304,65 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91992991</t>
+          <t>https://artportalen.se/Sighting/126348501</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136828022</v>
+        <v>126348502</v>
       </c>
       <c r="B8" t="n">
-        <v>80595</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Digerberget, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>412377</v>
+        <v>412740</v>
       </c>
       <c r="R8" t="n">
-        <v>6965984</v>
+        <v>6965691</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1361,12 +1386,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1381,24 +1411,24 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136828022</t>
+          <t>https://artportalen.se/Sighting/126348502</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126348497</v>
+        <v>126348503</v>
       </c>
       <c r="B9" t="n">
         <v>57953</v>
@@ -1433,10 +1463,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>412701</v>
+        <v>412816</v>
       </c>
       <c r="R9" t="n">
-        <v>6965749</v>
+        <v>6965745</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1473,7 +1503,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1499,13 +1529,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348497</t>
+          <t>https://artportalen.se/Sighting/126348503</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126348498</v>
+        <v>126348505</v>
       </c>
       <c r="B10" t="n">
         <v>57953</v>
@@ -1540,10 +1570,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>412636</v>
+        <v>412820</v>
       </c>
       <c r="R10" t="n">
-        <v>6965623</v>
+        <v>6965733</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1580,7 +1610,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1606,1062 +1636,7 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348498</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>126348499</v>
-      </c>
-      <c r="B11" t="n">
-        <v>57953</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Digerberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>412630</v>
-      </c>
-      <c r="R11" t="n">
-        <v>6965613</v>
-      </c>
-      <c r="S11" t="n">
-        <v>10</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/126348499</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>126348500</v>
-      </c>
-      <c r="B12" t="n">
-        <v>57953</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Digerberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>412646</v>
-      </c>
-      <c r="R12" t="n">
-        <v>6965606</v>
-      </c>
-      <c r="S12" t="n">
-        <v>10</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/126348500</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>126348501</v>
-      </c>
-      <c r="B13" t="n">
-        <v>57953</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Digerberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
-        <v>412693</v>
-      </c>
-      <c r="R13" t="n">
-        <v>6965664</v>
-      </c>
-      <c r="S13" t="n">
-        <v>10</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/126348501</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>126348502</v>
-      </c>
-      <c r="B14" t="n">
-        <v>57953</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Digerberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>412740</v>
-      </c>
-      <c r="R14" t="n">
-        <v>6965691</v>
-      </c>
-      <c r="S14" t="n">
-        <v>10</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/126348502</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>126348503</v>
-      </c>
-      <c r="B15" t="n">
-        <v>57953</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Digerberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>412816</v>
-      </c>
-      <c r="R15" t="n">
-        <v>6965745</v>
-      </c>
-      <c r="S15" t="n">
-        <v>10</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/126348503</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>126348505</v>
-      </c>
-      <c r="B16" t="n">
-        <v>57953</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Digerberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>412820</v>
-      </c>
-      <c r="R16" t="n">
-        <v>6965733</v>
-      </c>
-      <c r="S16" t="n">
-        <v>10</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
-      <c r="AZ16" t="inlineStr">
-        <is>
           <t>https://artportalen.se/Sighting/126348505</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>136828018</v>
-      </c>
-      <c r="B17" t="n">
-        <v>58169</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>412709</v>
-      </c>
-      <c r="R17" t="n">
-        <v>6965881</v>
-      </c>
-      <c r="S17" t="n">
-        <v>5</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136828018</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>136828014</v>
-      </c>
-      <c r="B18" t="n">
-        <v>79499</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>412914</v>
-      </c>
-      <c r="R18" t="n">
-        <v>6965758</v>
-      </c>
-      <c r="S18" t="n">
-        <v>5</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136828014</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>136828017</v>
-      </c>
-      <c r="B19" t="n">
-        <v>79499</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q19" t="n">
-        <v>412708</v>
-      </c>
-      <c r="R19" t="n">
-        <v>6965886</v>
-      </c>
-      <c r="S19" t="n">
-        <v>10</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136828017</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>136828024</v>
-      </c>
-      <c r="B20" t="n">
-        <v>79499</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q20" t="n">
-        <v>412344</v>
-      </c>
-      <c r="R20" t="n">
-        <v>6966001</v>
-      </c>
-      <c r="S20" t="n">
-        <v>5</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="inlineStr"/>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136828024</t>
         </is>
       </c>
     </row>
@@ -2676,16 +1651,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21370-2025 artfynd.xlsx
+++ b/artfynd/A 21370-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828020</v>
       </c>
       <c r="B2" t="n">
-        <v>92292</v>
+        <v>92294</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136828015</v>
       </c>
       <c r="B3" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136828019</v>
       </c>
       <c r="B4" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136828023</v>
       </c>
       <c r="B5" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136828021</v>
       </c>
       <c r="B6" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>136828022</v>
       </c>
       <c r="B8" t="n">
-        <v>80595</v>
+        <v>80599</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>136828014</v>
       </c>
       <c r="B18" t="n">
-        <v>79499</v>
+        <v>79503</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
         <v>136828017</v>
       </c>
       <c r="B19" t="n">
-        <v>79499</v>
+        <v>79503</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>136828024</v>
       </c>
       <c r="B20" t="n">
-        <v>79499</v>
+        <v>79503</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 21370-2025 artfynd.xlsx
+++ b/artfynd/A 21370-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828020</v>
       </c>
       <c r="B2" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136828015</v>
       </c>
       <c r="B3" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136828019</v>
       </c>
       <c r="B4" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136828023</v>
       </c>
       <c r="B5" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136828021</v>
       </c>
       <c r="B6" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>136828022</v>
       </c>
       <c r="B8" t="n">
-        <v>80599</v>
+        <v>80601</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>136828014</v>
       </c>
       <c r="B18" t="n">
-        <v>79503</v>
+        <v>79505</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
         <v>136828017</v>
       </c>
       <c r="B19" t="n">
-        <v>79503</v>
+        <v>79505</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>136828024</v>
       </c>
       <c r="B20" t="n">
-        <v>79503</v>
+        <v>79505</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 21370-2025 artfynd.xlsx
+++ b/artfynd/A 21370-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828020</v>
       </c>
       <c r="B2" t="n">
-        <v>92296</v>
+        <v>92297</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136828015</v>
       </c>
       <c r="B3" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136828019</v>
       </c>
       <c r="B4" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136828023</v>
       </c>
       <c r="B5" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136828021</v>
       </c>
       <c r="B6" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>136828022</v>
       </c>
       <c r="B8" t="n">
-        <v>80601</v>
+        <v>80602</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>136828014</v>
       </c>
       <c r="B18" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
         <v>136828017</v>
       </c>
       <c r="B19" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>136828024</v>
       </c>
       <c r="B20" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 21370-2025 artfynd.xlsx
+++ b/artfynd/A 21370-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828020</v>
       </c>
       <c r="B2" t="n">
-        <v>92297</v>
+        <v>92303</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136828015</v>
       </c>
       <c r="B3" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136828019</v>
       </c>
       <c r="B4" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 21370-2025 artfynd.xlsx
+++ b/artfynd/A 21370-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ20"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>136828020</v>
+        <v>91992991</v>
       </c>
       <c r="B2" t="n">
-        <v>92303</v>
+        <v>79084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Jämtlands län, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>412592</v>
+        <v>412616</v>
       </c>
       <c r="R2" t="n">
-        <v>6965947</v>
+        <v>6966018</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2018-06-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2018-10-31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,27 +765,31 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136828020</t>
+          <t>https://artportalen.se/Sighting/91992991</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136828015</v>
+        <v>126348497</v>
       </c>
       <c r="B3" t="n">
-        <v>93434</v>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,37 +797,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4366</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Digerberget, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>412878</v>
+        <v>412701</v>
       </c>
       <c r="R3" t="n">
-        <v>6965808</v>
+        <v>6965749</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +851,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,65 +876,65 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136828015</t>
+          <t>https://artportalen.se/Sighting/126348497</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136828019</v>
+        <v>126348498</v>
       </c>
       <c r="B4" t="n">
-        <v>92087</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Digerberget, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>412577</v>
+        <v>412636</v>
       </c>
       <c r="R4" t="n">
-        <v>6965950</v>
+        <v>6965623</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -949,12 +958,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,65 +983,65 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136828019</t>
+          <t>https://artportalen.se/Sighting/126348498</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136828023</v>
+        <v>126348499</v>
       </c>
       <c r="B5" t="n">
-        <v>79483</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Digerberget, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>412364</v>
+        <v>412630</v>
       </c>
       <c r="R5" t="n">
-        <v>6965991</v>
+        <v>6965613</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,12 +1065,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,27 +1090,27 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136828023</t>
+          <t>https://artportalen.se/Sighting/126348499</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136828021</v>
+        <v>126348500</v>
       </c>
       <c r="B6" t="n">
-        <v>78886</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,37 +1118,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Digerberget, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>412533</v>
+        <v>412646</v>
       </c>
       <c r="R6" t="n">
-        <v>6965932</v>
+        <v>6965606</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1153,12 +1172,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,27 +1197,27 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136828021</t>
+          <t>https://artportalen.se/Sighting/126348500</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>91992991</v>
+        <v>126348501</v>
       </c>
       <c r="B7" t="n">
-        <v>79084</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,37 +1225,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Jämtlands län, Hjd</t>
+          <t>Digerberget, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>412616</v>
+        <v>412693</v>
       </c>
       <c r="R7" t="n">
-        <v>6966018</v>
+        <v>6965664</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1255,12 +1279,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2018-06-01</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2018-10-31</t>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1275,69 +1304,65 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91992991</t>
+          <t>https://artportalen.se/Sighting/126348501</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136828022</v>
+        <v>126348502</v>
       </c>
       <c r="B8" t="n">
-        <v>80602</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Digerberget, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>412377</v>
+        <v>412740</v>
       </c>
       <c r="R8" t="n">
-        <v>6965984</v>
+        <v>6965691</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1361,12 +1386,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1381,24 +1411,24 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136828022</t>
+          <t>https://artportalen.se/Sighting/126348502</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126348497</v>
+        <v>126348503</v>
       </c>
       <c r="B9" t="n">
         <v>57953</v>
@@ -1433,10 +1463,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>412701</v>
+        <v>412816</v>
       </c>
       <c r="R9" t="n">
-        <v>6965749</v>
+        <v>6965745</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1473,7 +1503,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1499,13 +1529,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348497</t>
+          <t>https://artportalen.se/Sighting/126348503</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126348498</v>
+        <v>126348505</v>
       </c>
       <c r="B10" t="n">
         <v>57953</v>
@@ -1540,10 +1570,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>412636</v>
+        <v>412820</v>
       </c>
       <c r="R10" t="n">
-        <v>6965623</v>
+        <v>6965733</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1580,7 +1610,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1606,1062 +1636,7 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348498</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>126348499</v>
-      </c>
-      <c r="B11" t="n">
-        <v>57953</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Digerberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>412630</v>
-      </c>
-      <c r="R11" t="n">
-        <v>6965613</v>
-      </c>
-      <c r="S11" t="n">
-        <v>10</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/126348499</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>126348500</v>
-      </c>
-      <c r="B12" t="n">
-        <v>57953</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Digerberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>412646</v>
-      </c>
-      <c r="R12" t="n">
-        <v>6965606</v>
-      </c>
-      <c r="S12" t="n">
-        <v>10</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/126348500</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>126348501</v>
-      </c>
-      <c r="B13" t="n">
-        <v>57953</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Digerberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
-        <v>412693</v>
-      </c>
-      <c r="R13" t="n">
-        <v>6965664</v>
-      </c>
-      <c r="S13" t="n">
-        <v>10</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/126348501</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>126348502</v>
-      </c>
-      <c r="B14" t="n">
-        <v>57953</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Digerberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>412740</v>
-      </c>
-      <c r="R14" t="n">
-        <v>6965691</v>
-      </c>
-      <c r="S14" t="n">
-        <v>10</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/126348502</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>126348503</v>
-      </c>
-      <c r="B15" t="n">
-        <v>57953</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Digerberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>412816</v>
-      </c>
-      <c r="R15" t="n">
-        <v>6965745</v>
-      </c>
-      <c r="S15" t="n">
-        <v>10</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/126348503</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>126348505</v>
-      </c>
-      <c r="B16" t="n">
-        <v>57953</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Digerberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>412820</v>
-      </c>
-      <c r="R16" t="n">
-        <v>6965733</v>
-      </c>
-      <c r="S16" t="n">
-        <v>10</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
-      <c r="AZ16" t="inlineStr">
-        <is>
           <t>https://artportalen.se/Sighting/126348505</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>136828018</v>
-      </c>
-      <c r="B17" t="n">
-        <v>58169</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>412709</v>
-      </c>
-      <c r="R17" t="n">
-        <v>6965881</v>
-      </c>
-      <c r="S17" t="n">
-        <v>5</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136828018</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>136828014</v>
-      </c>
-      <c r="B18" t="n">
-        <v>79506</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>412914</v>
-      </c>
-      <c r="R18" t="n">
-        <v>6965758</v>
-      </c>
-      <c r="S18" t="n">
-        <v>5</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136828014</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>136828017</v>
-      </c>
-      <c r="B19" t="n">
-        <v>79506</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q19" t="n">
-        <v>412708</v>
-      </c>
-      <c r="R19" t="n">
-        <v>6965886</v>
-      </c>
-      <c r="S19" t="n">
-        <v>10</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136828017</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>136828024</v>
-      </c>
-      <c r="B20" t="n">
-        <v>79506</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q20" t="n">
-        <v>412344</v>
-      </c>
-      <c r="R20" t="n">
-        <v>6966001</v>
-      </c>
-      <c r="S20" t="n">
-        <v>5</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="inlineStr"/>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136828024</t>
         </is>
       </c>
     </row>
@@ -2676,16 +1651,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21370-2025 artfynd.xlsx
+++ b/artfynd/A 21370-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ10"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>91992991</v>
+        <v>136828020</v>
       </c>
       <c r="B2" t="n">
-        <v>79084</v>
+        <v>92307</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Jämtlands län, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>412616</v>
+        <v>412592</v>
       </c>
       <c r="R2" t="n">
-        <v>6966018</v>
+        <v>6965947</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-06-01</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-10-31</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,31 +765,27 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91992991</t>
+          <t>https://artportalen.se/Sighting/136828020</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126348497</v>
+        <v>136828015</v>
       </c>
       <c r="B3" t="n">
-        <v>57953</v>
+        <v>93438</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>4366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Digerberget, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>412701</v>
+        <v>412878</v>
       </c>
       <c r="R3" t="n">
-        <v>6965749</v>
+        <v>6965808</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -851,17 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -876,65 +867,65 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348497</t>
+          <t>https://artportalen.se/Sighting/136828015</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126348498</v>
+        <v>136828019</v>
       </c>
       <c r="B4" t="n">
-        <v>57953</v>
+        <v>92091</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Digerberget, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>412636</v>
+        <v>412577</v>
       </c>
       <c r="R4" t="n">
-        <v>6965623</v>
+        <v>6965950</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -958,17 +949,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -983,65 +969,65 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348498</t>
+          <t>https://artportalen.se/Sighting/136828019</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126348499</v>
+        <v>136828023</v>
       </c>
       <c r="B5" t="n">
-        <v>57953</v>
+        <v>79485</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Digerberget, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>412630</v>
+        <v>412364</v>
       </c>
       <c r="R5" t="n">
-        <v>6965613</v>
+        <v>6965991</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1065,17 +1051,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1090,27 +1071,27 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348499</t>
+          <t>https://artportalen.se/Sighting/136828023</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126348500</v>
+        <v>136828021</v>
       </c>
       <c r="B6" t="n">
-        <v>57953</v>
+        <v>78888</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1118,37 +1099,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Digerberget, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>412646</v>
+        <v>412533</v>
       </c>
       <c r="R6" t="n">
-        <v>6965606</v>
+        <v>6965932</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1172,17 +1153,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1197,27 +1173,27 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348500</t>
+          <t>https://artportalen.se/Sighting/136828021</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126348501</v>
+        <v>91992991</v>
       </c>
       <c r="B7" t="n">
-        <v>57953</v>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1225,37 +1201,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Digerberget, Hjd</t>
+          <t>Jämtlands län, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>412693</v>
+        <v>412616</v>
       </c>
       <c r="R7" t="n">
-        <v>6965664</v>
+        <v>6966018</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1279,17 +1255,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2018-06-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2018-10-31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1304,65 +1275,69 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348501</t>
+          <t>https://artportalen.se/Sighting/91992991</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126348502</v>
+        <v>136828022</v>
       </c>
       <c r="B8" t="n">
-        <v>57953</v>
+        <v>80604</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Digerberget, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>412740</v>
+        <v>412377</v>
       </c>
       <c r="R8" t="n">
-        <v>6965691</v>
+        <v>6965984</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1386,17 +1361,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1411,24 +1381,24 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348502</t>
+          <t>https://artportalen.se/Sighting/136828022</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126348503</v>
+        <v>126348497</v>
       </c>
       <c r="B9" t="n">
         <v>57953</v>
@@ -1463,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>412816</v>
+        <v>412701</v>
       </c>
       <c r="R9" t="n">
-        <v>6965745</v>
+        <v>6965749</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1503,7 +1473,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1529,13 +1499,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348503</t>
+          <t>https://artportalen.se/Sighting/126348497</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126348505</v>
+        <v>126348498</v>
       </c>
       <c r="B10" t="n">
         <v>57953</v>
@@ -1570,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>412820</v>
+        <v>412636</v>
       </c>
       <c r="R10" t="n">
-        <v>6965733</v>
+        <v>6965623</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1610,7 +1580,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1636,7 +1606,1062 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/126348498</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126348499</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Digerberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>412630</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6965613</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348499</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126348500</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Digerberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>412646</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6965606</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348500</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126348501</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Digerberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>412693</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6965664</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348501</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>126348502</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Digerberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>412740</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6965691</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348502</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>126348503</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Digerberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>412816</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6965745</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348503</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>126348505</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Digerberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>412820</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6965733</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/126348505</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>136828018</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>412709</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6965881</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828018</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136828014</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79508</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>412914</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6965758</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828014</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136828017</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79508</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>412708</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6965886</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828017</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>136828024</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79508</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>412344</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6966001</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828024</t>
         </is>
       </c>
     </row>
@@ -1651,6 +2676,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21370-2025 artfynd.xlsx
+++ b/artfynd/A 21370-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ20"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>136828020</v>
+        <v>91992991</v>
       </c>
       <c r="B2" t="n">
-        <v>92307</v>
+        <v>79084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Jämtlands län, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>412592</v>
+        <v>412616</v>
       </c>
       <c r="R2" t="n">
-        <v>6965947</v>
+        <v>6966018</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2018-06-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2018-10-31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,27 +765,31 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136828020</t>
+          <t>https://artportalen.se/Sighting/91992991</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136828015</v>
+        <v>126348497</v>
       </c>
       <c r="B3" t="n">
-        <v>93438</v>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,37 +797,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4366</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Digerberget, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>412878</v>
+        <v>412701</v>
       </c>
       <c r="R3" t="n">
-        <v>6965808</v>
+        <v>6965749</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +851,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,65 +876,65 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136828015</t>
+          <t>https://artportalen.se/Sighting/126348497</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136828019</v>
+        <v>126348498</v>
       </c>
       <c r="B4" t="n">
-        <v>92091</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Digerberget, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>412577</v>
+        <v>412636</v>
       </c>
       <c r="R4" t="n">
-        <v>6965950</v>
+        <v>6965623</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -949,12 +958,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,65 +983,65 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136828019</t>
+          <t>https://artportalen.se/Sighting/126348498</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136828023</v>
+        <v>126348499</v>
       </c>
       <c r="B5" t="n">
-        <v>79485</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Digerberget, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>412364</v>
+        <v>412630</v>
       </c>
       <c r="R5" t="n">
-        <v>6965991</v>
+        <v>6965613</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,12 +1065,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,27 +1090,27 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136828023</t>
+          <t>https://artportalen.se/Sighting/126348499</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136828021</v>
+        <v>126348500</v>
       </c>
       <c r="B6" t="n">
-        <v>78888</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,37 +1118,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Digerberget, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>412533</v>
+        <v>412646</v>
       </c>
       <c r="R6" t="n">
-        <v>6965932</v>
+        <v>6965606</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1153,12 +1172,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,27 +1197,27 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136828021</t>
+          <t>https://artportalen.se/Sighting/126348500</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>91992991</v>
+        <v>126348501</v>
       </c>
       <c r="B7" t="n">
-        <v>79084</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,37 +1225,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Jämtlands län, Hjd</t>
+          <t>Digerberget, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>412616</v>
+        <v>412693</v>
       </c>
       <c r="R7" t="n">
-        <v>6966018</v>
+        <v>6965664</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1255,12 +1279,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2018-06-01</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2018-10-31</t>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1275,69 +1304,65 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91992991</t>
+          <t>https://artportalen.se/Sighting/126348501</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136828022</v>
+        <v>126348502</v>
       </c>
       <c r="B8" t="n">
-        <v>80604</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Digerberget, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>412377</v>
+        <v>412740</v>
       </c>
       <c r="R8" t="n">
-        <v>6965984</v>
+        <v>6965691</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1361,12 +1386,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1381,24 +1411,24 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136828022</t>
+          <t>https://artportalen.se/Sighting/126348502</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126348497</v>
+        <v>126348503</v>
       </c>
       <c r="B9" t="n">
         <v>57953</v>
@@ -1433,10 +1463,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>412701</v>
+        <v>412816</v>
       </c>
       <c r="R9" t="n">
-        <v>6965749</v>
+        <v>6965745</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1473,7 +1503,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1499,13 +1529,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348497</t>
+          <t>https://artportalen.se/Sighting/126348503</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126348498</v>
+        <v>126348505</v>
       </c>
       <c r="B10" t="n">
         <v>57953</v>
@@ -1540,10 +1570,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>412636</v>
+        <v>412820</v>
       </c>
       <c r="R10" t="n">
-        <v>6965623</v>
+        <v>6965733</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1580,7 +1610,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1606,1062 +1636,7 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348498</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>126348499</v>
-      </c>
-      <c r="B11" t="n">
-        <v>57953</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Digerberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>412630</v>
-      </c>
-      <c r="R11" t="n">
-        <v>6965613</v>
-      </c>
-      <c r="S11" t="n">
-        <v>10</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/126348499</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>126348500</v>
-      </c>
-      <c r="B12" t="n">
-        <v>57953</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Digerberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>412646</v>
-      </c>
-      <c r="R12" t="n">
-        <v>6965606</v>
-      </c>
-      <c r="S12" t="n">
-        <v>10</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/126348500</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>126348501</v>
-      </c>
-      <c r="B13" t="n">
-        <v>57953</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Digerberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
-        <v>412693</v>
-      </c>
-      <c r="R13" t="n">
-        <v>6965664</v>
-      </c>
-      <c r="S13" t="n">
-        <v>10</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/126348501</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>126348502</v>
-      </c>
-      <c r="B14" t="n">
-        <v>57953</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Digerberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>412740</v>
-      </c>
-      <c r="R14" t="n">
-        <v>6965691</v>
-      </c>
-      <c r="S14" t="n">
-        <v>10</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/126348502</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>126348503</v>
-      </c>
-      <c r="B15" t="n">
-        <v>57953</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Digerberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>412816</v>
-      </c>
-      <c r="R15" t="n">
-        <v>6965745</v>
-      </c>
-      <c r="S15" t="n">
-        <v>10</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/126348503</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>126348505</v>
-      </c>
-      <c r="B16" t="n">
-        <v>57953</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Digerberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>412820</v>
-      </c>
-      <c r="R16" t="n">
-        <v>6965733</v>
-      </c>
-      <c r="S16" t="n">
-        <v>10</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
-      <c r="AZ16" t="inlineStr">
-        <is>
           <t>https://artportalen.se/Sighting/126348505</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>136828018</v>
-      </c>
-      <c r="B17" t="n">
-        <v>58169</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>412709</v>
-      </c>
-      <c r="R17" t="n">
-        <v>6965881</v>
-      </c>
-      <c r="S17" t="n">
-        <v>5</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136828018</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>136828014</v>
-      </c>
-      <c r="B18" t="n">
-        <v>79508</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>412914</v>
-      </c>
-      <c r="R18" t="n">
-        <v>6965758</v>
-      </c>
-      <c r="S18" t="n">
-        <v>5</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136828014</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>136828017</v>
-      </c>
-      <c r="B19" t="n">
-        <v>79508</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q19" t="n">
-        <v>412708</v>
-      </c>
-      <c r="R19" t="n">
-        <v>6965886</v>
-      </c>
-      <c r="S19" t="n">
-        <v>10</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136828017</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>136828024</v>
-      </c>
-      <c r="B20" t="n">
-        <v>79508</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Långtjärnberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q20" t="n">
-        <v>412344</v>
-      </c>
-      <c r="R20" t="n">
-        <v>6966001</v>
-      </c>
-      <c r="S20" t="n">
-        <v>5</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AD20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="inlineStr"/>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136828024</t>
         </is>
       </c>
     </row>
@@ -2676,16 +1651,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21370-2025 artfynd.xlsx
+++ b/artfynd/A 21370-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ10"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>91992991</v>
+        <v>136828020</v>
       </c>
       <c r="B2" t="n">
-        <v>79084</v>
+        <v>92309</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Jämtlands län, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>412616</v>
+        <v>412592</v>
       </c>
       <c r="R2" t="n">
-        <v>6966018</v>
+        <v>6965947</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-06-01</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-10-31</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,31 +765,27 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91992991</t>
+          <t>https://artportalen.se/Sighting/136828020</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126348497</v>
+        <v>136828015</v>
       </c>
       <c r="B3" t="n">
-        <v>57953</v>
+        <v>93440</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>4366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Digerberget, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>412701</v>
+        <v>412878</v>
       </c>
       <c r="R3" t="n">
-        <v>6965749</v>
+        <v>6965808</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -851,17 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -876,65 +867,65 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348497</t>
+          <t>https://artportalen.se/Sighting/136828015</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126348498</v>
+        <v>136828019</v>
       </c>
       <c r="B4" t="n">
-        <v>57953</v>
+        <v>92093</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Digerberget, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>412636</v>
+        <v>412577</v>
       </c>
       <c r="R4" t="n">
-        <v>6965623</v>
+        <v>6965950</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -958,17 +949,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -983,65 +969,65 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348498</t>
+          <t>https://artportalen.se/Sighting/136828019</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126348499</v>
+        <v>136828023</v>
       </c>
       <c r="B5" t="n">
-        <v>57953</v>
+        <v>79488</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Digerberget, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>412630</v>
+        <v>412364</v>
       </c>
       <c r="R5" t="n">
-        <v>6965613</v>
+        <v>6965991</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1065,17 +1051,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1090,27 +1071,27 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348499</t>
+          <t>https://artportalen.se/Sighting/136828023</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126348500</v>
+        <v>136828021</v>
       </c>
       <c r="B6" t="n">
-        <v>57953</v>
+        <v>78891</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1118,37 +1099,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Digerberget, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>412646</v>
+        <v>412533</v>
       </c>
       <c r="R6" t="n">
-        <v>6965606</v>
+        <v>6965932</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1172,17 +1153,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1197,27 +1173,27 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348500</t>
+          <t>https://artportalen.se/Sighting/136828021</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126348501</v>
+        <v>91992991</v>
       </c>
       <c r="B7" t="n">
-        <v>57953</v>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1225,37 +1201,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Digerberget, Hjd</t>
+          <t>Jämtlands län, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>412693</v>
+        <v>412616</v>
       </c>
       <c r="R7" t="n">
-        <v>6965664</v>
+        <v>6966018</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1279,17 +1255,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2018-06-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2018-10-31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1304,65 +1275,69 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348501</t>
+          <t>https://artportalen.se/Sighting/91992991</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126348502</v>
+        <v>136828022</v>
       </c>
       <c r="B8" t="n">
-        <v>57953</v>
+        <v>80607</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Digerberget, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>412740</v>
+        <v>412377</v>
       </c>
       <c r="R8" t="n">
-        <v>6965691</v>
+        <v>6965984</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1386,17 +1361,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1411,24 +1381,24 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348502</t>
+          <t>https://artportalen.se/Sighting/136828022</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126348503</v>
+        <v>126348497</v>
       </c>
       <c r="B9" t="n">
         <v>57953</v>
@@ -1463,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>412816</v>
+        <v>412701</v>
       </c>
       <c r="R9" t="n">
-        <v>6965745</v>
+        <v>6965749</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1503,7 +1473,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1529,13 +1499,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348503</t>
+          <t>https://artportalen.se/Sighting/126348497</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126348505</v>
+        <v>126348498</v>
       </c>
       <c r="B10" t="n">
         <v>57953</v>
@@ -1570,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>412820</v>
+        <v>412636</v>
       </c>
       <c r="R10" t="n">
-        <v>6965733</v>
+        <v>6965623</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1610,7 +1580,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1636,7 +1606,1062 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/126348498</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126348499</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Digerberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>412630</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6965613</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348499</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126348500</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Digerberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>412646</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6965606</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348500</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126348501</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Digerberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>412693</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6965664</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348501</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>126348502</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Digerberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>412740</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6965691</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348502</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>126348503</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Digerberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>412816</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6965745</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348503</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>126348505</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Digerberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>412820</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6965733</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/126348505</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>136828018</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>412709</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6965881</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828018</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136828014</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79511</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>412914</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6965758</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828014</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136828017</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79511</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>412708</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6965886</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828017</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>136828024</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79511</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>412344</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6966001</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828024</t>
         </is>
       </c>
     </row>
@@ -1651,6 +2676,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21370-2025 artfynd.xlsx
+++ b/artfynd/A 21370-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828020</v>
       </c>
       <c r="B2" t="n">
-        <v>92309</v>
+        <v>92322</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136828015</v>
       </c>
       <c r="B3" t="n">
-        <v>93440</v>
+        <v>93453</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136828019</v>
       </c>
       <c r="B4" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136828023</v>
       </c>
       <c r="B5" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136828021</v>
       </c>
       <c r="B6" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>136828022</v>
       </c>
       <c r="B8" t="n">
-        <v>80607</v>
+        <v>80620</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>136828018</v>
       </c>
       <c r="B17" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>136828014</v>
       </c>
       <c r="B18" t="n">
-        <v>79511</v>
+        <v>79524</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
         <v>136828017</v>
       </c>
       <c r="B19" t="n">
-        <v>79511</v>
+        <v>79524</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>136828024</v>
       </c>
       <c r="B20" t="n">
-        <v>79511</v>
+        <v>79524</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 21370-2025 artfynd.xlsx
+++ b/artfynd/A 21370-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828020</v>
       </c>
       <c r="B2" t="n">
-        <v>92322</v>
+        <v>92324</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136828015</v>
       </c>
       <c r="B3" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136828019</v>
       </c>
       <c r="B4" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136828023</v>
       </c>
       <c r="B5" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136828021</v>
       </c>
       <c r="B6" t="n">
-        <v>78904</v>
+        <v>78906</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>136828022</v>
       </c>
       <c r="B8" t="n">
-        <v>80620</v>
+        <v>80622</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>136828018</v>
       </c>
       <c r="B17" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>136828014</v>
       </c>
       <c r="B18" t="n">
-        <v>79524</v>
+        <v>79526</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
         <v>136828017</v>
       </c>
       <c r="B19" t="n">
-        <v>79524</v>
+        <v>79526</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>136828024</v>
       </c>
       <c r="B20" t="n">
-        <v>79524</v>
+        <v>79526</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 21370-2025 artfynd.xlsx
+++ b/artfynd/A 21370-2025 artfynd.xlsx
@@ -2283,11 +2283,7 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Långtjärnberget, Hjd</t>

--- a/artfynd/A 21370-2025 artfynd.xlsx
+++ b/artfynd/A 21370-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828020</v>
       </c>
       <c r="B2" t="n">
-        <v>92324</v>
+        <v>92327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136828015</v>
       </c>
       <c r="B3" t="n">
-        <v>93454</v>
+        <v>93457</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136828019</v>
       </c>
       <c r="B4" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 21370-2025 artfynd.xlsx
+++ b/artfynd/A 21370-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828020</v>
       </c>
       <c r="B2" t="n">
-        <v>92327</v>
+        <v>92337</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136828015</v>
       </c>
       <c r="B3" t="n">
-        <v>93457</v>
+        <v>93467</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136828019</v>
       </c>
       <c r="B4" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136828023</v>
       </c>
       <c r="B5" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136828021</v>
       </c>
       <c r="B6" t="n">
-        <v>78906</v>
+        <v>78916</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>136828022</v>
       </c>
       <c r="B8" t="n">
-        <v>80622</v>
+        <v>80632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>136828018</v>
       </c>
       <c r="B17" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         <v>136828014</v>
       </c>
       <c r="B18" t="n">
-        <v>79526</v>
+        <v>79536</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         <v>136828017</v>
       </c>
       <c r="B19" t="n">
-        <v>79526</v>
+        <v>79536</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
         <v>136828024</v>
       </c>
       <c r="B20" t="n">
-        <v>79526</v>
+        <v>79536</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 21370-2025 artfynd.xlsx
+++ b/artfynd/A 21370-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828020</v>
       </c>
       <c r="B2" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136828015</v>
       </c>
       <c r="B3" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136828019</v>
       </c>
       <c r="B4" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 21370-2025 artfynd.xlsx
+++ b/artfynd/A 21370-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828020</v>
       </c>
       <c r="B2" t="n">
-        <v>92338</v>
+        <v>92341</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136828015</v>
       </c>
       <c r="B3" t="n">
-        <v>93468</v>
+        <v>93473</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136828019</v>
       </c>
       <c r="B4" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136828023</v>
       </c>
       <c r="B5" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136828021</v>
       </c>
       <c r="B6" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>136828022</v>
       </c>
       <c r="B8" t="n">
-        <v>80632</v>
+        <v>80635</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>136828018</v>
       </c>
       <c r="B17" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         <v>136828014</v>
       </c>
       <c r="B18" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         <v>136828017</v>
       </c>
       <c r="B19" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
         <v>136828024</v>
       </c>
       <c r="B20" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 21370-2025 artfynd.xlsx
+++ b/artfynd/A 21370-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828020</v>
       </c>
       <c r="B2" t="n">
-        <v>92341</v>
+        <v>92343</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136828015</v>
       </c>
       <c r="B3" t="n">
-        <v>93473</v>
+        <v>93475</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136828019</v>
       </c>
       <c r="B4" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 21370-2025 artfynd.xlsx
+++ b/artfynd/A 21370-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828020</v>
       </c>
       <c r="B2" t="n">
-        <v>92343</v>
+        <v>92348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136828015</v>
       </c>
       <c r="B3" t="n">
-        <v>93475</v>
+        <v>93481</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136828019</v>
       </c>
       <c r="B4" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136828023</v>
       </c>
       <c r="B5" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136828021</v>
       </c>
       <c r="B6" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>136828022</v>
       </c>
       <c r="B8" t="n">
-        <v>80635</v>
+        <v>80640</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>136828018</v>
       </c>
       <c r="B17" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         <v>136828014</v>
       </c>
       <c r="B18" t="n">
-        <v>79539</v>
+        <v>79544</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         <v>136828017</v>
       </c>
       <c r="B19" t="n">
-        <v>79539</v>
+        <v>79544</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
         <v>136828024</v>
       </c>
       <c r="B20" t="n">
-        <v>79539</v>
+        <v>79544</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 21370-2025 artfynd.xlsx
+++ b/artfynd/A 21370-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828020</v>
       </c>
       <c r="B2" t="n">
-        <v>92348</v>
+        <v>92360</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136828015</v>
       </c>
       <c r="B3" t="n">
-        <v>93481</v>
+        <v>93493</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136828019</v>
       </c>
       <c r="B4" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136828023</v>
       </c>
       <c r="B5" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136828021</v>
       </c>
       <c r="B6" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>136828022</v>
       </c>
       <c r="B8" t="n">
-        <v>80640</v>
+        <v>80651</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         <v>136828014</v>
       </c>
       <c r="B18" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         <v>136828017</v>
       </c>
       <c r="B19" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
         <v>136828024</v>
       </c>
       <c r="B20" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
